--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -52,9 +52,6 @@
     <t>Desc</t>
   </si>
   <si>
-    <t>Radius</t>
-  </si>
-  <si>
     <t>!string</t>
   </si>
   <si>
@@ -63,22 +60,6 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>float</t>
-    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -770,27 +751,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -801,7 +782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -812,15 +793,14 @@
     <col min="6" max="6" width="26.125" style="2" customWidth="1"/>
     <col min="7" max="7" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -828,16 +808,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>4</v>
@@ -846,279 +826,252 @@
         <v>5</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="I3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="6">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H4" s="6">
         <v>1001</v>
       </c>
       <c r="I4" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="J4" s="6">
         <v>101</v>
       </c>
-      <c r="K4" s="14">
+      <c r="J4" s="14">
         <v>1001</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="6">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H5" s="6">
         <v>2001</v>
       </c>
-      <c r="I5" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="I5" s="2">
         <v>201</v>
       </c>
-      <c r="K5">
+      <c r="J5">
         <v>1001</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2">
         <v>2002</v>
       </c>
-      <c r="I6" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="J6" s="2">
+      <c r="I6" s="2">
         <v>202</v>
       </c>
-      <c r="K6">
+      <c r="J6">
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2">
         <v>3001</v>
       </c>
-      <c r="I7" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="I7" s="2">
         <v>301</v>
       </c>
-      <c r="K7">
+      <c r="J7">
         <v>1001</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H8" s="6">
         <v>3002</v>
       </c>
-      <c r="I8" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="J8" s="2">
+      <c r="I8" s="2">
         <v>302</v>
       </c>
-      <c r="K8">
+      <c r="J8">
         <v>1001</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9" s="6">
         <v>4001</v>
       </c>
-      <c r="I9" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="J9" s="2">
+      <c r="I9" s="2">
         <v>401</v>
       </c>
-      <c r="K9">
+      <c r="J9">
         <v>1001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <v>2</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H10" s="6">
         <v>4002</v>
       </c>
-      <c r="I10" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="J10" s="2">
+      <c r="I10" s="2">
         <v>402</v>
       </c>
-      <c r="K10">
+      <c r="J10">
         <v>1001</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E11" s="7"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -148,15 +148,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillSetID</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -223,6 +215,62 @@
   </si>
   <si>
     <t>Prefab_Hero_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_1</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpecialSkill_2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseAttackSkill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PassiveSkill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CLASS_BASIC_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>기사</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>광전사</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>마검사</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -409,7 +457,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -448,7 +496,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -727,7 +774,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -751,12 +798,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -782,7 +829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -794,13 +841,13 @@
     <col min="7" max="7" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="10" max="10" width="21.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="21.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -808,7 +855,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>3</v>
@@ -825,20 +872,29 @@
       <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>34</v>
+      <c r="G2" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>7</v>
@@ -855,8 +911,8 @@
       <c r="F3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>35</v>
+      <c r="G3" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>8</v>
@@ -864,17 +920,26 @@
       <c r="I3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="6">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -883,7 +948,7 @@
         <v>11</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H4" s="6">
         <v>1001</v>
@@ -891,17 +956,26 @@
       <c r="I4" s="6">
         <v>101</v>
       </c>
-      <c r="J4" s="14">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="6">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -913,7 +987,7 @@
         <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5" s="6">
         <v>2001</v>
@@ -921,11 +995,8 @@
       <c r="I5" s="2">
         <v>201</v>
       </c>
-      <c r="J5">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>3</v>
       </c>
@@ -942,7 +1013,7 @@
         <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H6" s="2">
         <v>2002</v>
@@ -950,11 +1021,8 @@
       <c r="I6" s="2">
         <v>202</v>
       </c>
-      <c r="J6">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>4</v>
       </c>
@@ -971,7 +1039,7 @@
         <v>12</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2">
         <v>3001</v>
@@ -979,11 +1047,8 @@
       <c r="I7" s="2">
         <v>301</v>
       </c>
-      <c r="J7">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>5</v>
       </c>
@@ -1000,7 +1065,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8" s="6">
         <v>3002</v>
@@ -1008,11 +1073,8 @@
       <c r="I8" s="2">
         <v>302</v>
       </c>
-      <c r="J8">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>6</v>
       </c>
@@ -1029,19 +1091,16 @@
         <v>13</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H9" s="6">
-        <v>4001</v>
-      </c>
-      <c r="I9" s="2">
-        <v>401</v>
-      </c>
-      <c r="J9">
         <v>1001</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I9" s="6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6">
         <v>7</v>
@@ -1059,7 +1118,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H10" s="6">
         <v>4002</v>
@@ -1067,18 +1126,87 @@
       <c r="I10" s="2">
         <v>402</v>
       </c>
-      <c r="J10">
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>101</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="6">
         <v>1001</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E11" s="7"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E18"/>
+      <c r="I11" s="6">
+        <v>101</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>102</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1001</v>
+      </c>
+      <c r="I12" s="6">
+        <v>102</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>103</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1001</v>
+      </c>
+      <c r="I13" s="6">
+        <v>103</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -218,42 +218,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialSkill_2</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseAttackSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>PassiveSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_CLASS_BASIC_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>기사</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -266,11 +230,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
+    <t>BaseSkillSet</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -774,7 +738,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -829,7 +793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="10"/>
@@ -841,13 +805,11 @@
     <col min="7" max="7" width="15.125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="21.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="10" max="10" width="10.5" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
@@ -855,7 +817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="6" t="s">
         <v>3</v>
@@ -882,19 +844,10 @@
         <v>27</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="12" t="s">
         <v>7</v>
@@ -921,19 +874,10 @@
         <v>26</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="6">
         <v>1</v>
@@ -956,20 +900,9 @@
       <c r="I4" s="6">
         <v>101</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="6">
         <v>2</v>
@@ -996,7 +929,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>3</v>
       </c>
@@ -1022,7 +955,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>4</v>
       </c>
@@ -1048,7 +981,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>5</v>
       </c>
@@ -1074,7 +1007,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>6</v>
       </c>
@@ -1099,8 +1032,9 @@
       <c r="I9" s="6">
         <v>101</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="6">
         <v>7</v>
@@ -1127,7 +1061,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>101</v>
       </c>
@@ -1135,10 +1069,10 @@
         <v>30</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -1149,11 +1083,11 @@
       <c r="I11" s="6">
         <v>101</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J11" s="6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>102</v>
       </c>
@@ -1161,10 +1095,10 @@
         <v>15</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -1175,11 +1109,11 @@
       <c r="I12" s="6">
         <v>102</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J12" s="6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>103</v>
       </c>
@@ -1187,10 +1121,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -1201,8 +1135,8 @@
       <c r="I13" s="6">
         <v>103</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>48</v>
+      <c r="J13" s="6">
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -738,7 +738,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -31,10 +31,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -56,100 +56,47 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!CharacterTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CharacterClass</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>견습 기사</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>대검</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>룬블레이드</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Class_Knight</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Class_Berserker</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Class_RuneBlader</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>기사(2차)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>기사(1차)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>검방패</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>광전사(1차)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>광전사(2차)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>마검사(1차)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>마검사(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2차)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>ClassGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -165,19 +112,19 @@
       </rPr>
       <t>ID</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Class_Basic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Class_Knight</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>CharacterTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -194,7 +141,7 @@
       </rPr>
       <t>ath</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -211,51 +158,43 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Hero_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>기사</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>광전사</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>마검사</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BaseSkillSet</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -308,14 +247,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -413,15 +344,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -435,29 +366,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -738,7 +663,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -762,41 +687,41 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="10"/>
+    <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="28.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
@@ -809,341 +734,157 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="8"/>
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2">
+        <v>101</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1001</v>
+      </c>
+      <c r="I4" s="5">
+        <v>101</v>
+      </c>
+      <c r="J4" s="5">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2">
+        <v>102</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1001</v>
+      </c>
+      <c r="I5" s="5">
+        <v>102</v>
+      </c>
+      <c r="J5" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>103</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
+        <v>103</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="G6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="6">
+      <c r="H6" s="5">
         <v>1001</v>
       </c>
-      <c r="I4" s="6">
-        <v>101</v>
-      </c>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="6">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="6">
-        <v>2001</v>
-      </c>
-      <c r="I5" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="6">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2002</v>
-      </c>
-      <c r="I6" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="6">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="2">
-        <v>3001</v>
-      </c>
-      <c r="I7" s="2">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="6">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="6">
-        <v>3002</v>
-      </c>
-      <c r="I8" s="2">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="6">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1001</v>
-      </c>
-      <c r="I9" s="6">
-        <v>101</v>
-      </c>
-      <c r="J9" s="6"/>
+      <c r="I6" s="5">
+        <v>103</v>
+      </c>
+      <c r="J6" s="5">
+        <v>103</v>
+      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="6">
-        <v>4002</v>
-      </c>
-      <c r="I10" s="2">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="2">
-        <v>101</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="2">
-        <v>101</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1001</v>
-      </c>
-      <c r="I11" s="6">
-        <v>101</v>
-      </c>
-      <c r="J11" s="6">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="2">
-        <v>102</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="2">
-        <v>102</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="6">
-        <v>1001</v>
-      </c>
-      <c r="I12" s="6">
-        <v>102</v>
-      </c>
-      <c r="J12" s="6">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="2">
-        <v>103</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2">
-        <v>103</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="6">
-        <v>1001</v>
-      </c>
-      <c r="I13" s="6">
-        <v>103</v>
-      </c>
-      <c r="J13" s="6">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E17"/>
+      <c r="E10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -64,22 +64,6 @@
   </si>
   <si>
     <t>!CharacterTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterClass</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Knight</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Berserker</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_RuneBlader</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -112,14 +96,6 @@
       </rPr>
       <t>ID</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Basic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Knight</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -182,6 +158,22 @@
   </si>
   <si>
     <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Melee</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Ranged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterType</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -663,7 +655,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -671,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -687,27 +679,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -748,10 +735,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>4</v>
@@ -760,16 +747,16 @@
         <v>5</v>
       </c>
       <c r="G2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -781,7 +768,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>6</v>
@@ -790,16 +777,16 @@
         <v>6</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -807,16 +794,16 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2">
         <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H4" s="5">
         <v>1001</v>
@@ -833,16 +820,16 @@
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D5" s="2">
         <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H5" s="5">
         <v>1001</v>
@@ -859,16 +846,16 @@
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2">
         <v>103</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H6" s="5">
         <v>1001</v>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Character" sheetId="7" r:id="rId2"/>
+    <sheet name="#LevelExp" sheetId="9" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -64,14 +65,6 @@
   </si>
   <si>
     <t>!CharacterTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClassGrade</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -153,6 +146,54 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Melee</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Ranged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class1_SkillSet</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Melee</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class1_ReqLv</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class2_ReqLv</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class2_SkillSet</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelupStatID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>BaseSkillSet</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -161,19 +202,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Class_Melee</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Ranged</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Mage</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterType</t>
+    <t>LevelExp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalExperience</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -344,7 +377,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -378,6 +411,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -655,7 +691,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -679,22 +715,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -705,28 +741,236 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="28.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="26.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="21.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1001</v>
+      </c>
+      <c r="H4" s="5">
+        <v>101</v>
+      </c>
+      <c r="I4" s="5">
+        <v>101</v>
+      </c>
+      <c r="J4" s="5">
+        <v>101</v>
+      </c>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1001</v>
+      </c>
+      <c r="H5" s="5">
+        <v>102</v>
+      </c>
+      <c r="I5" s="5">
+        <v>102</v>
+      </c>
+      <c r="J5" s="5">
+        <v>102</v>
+      </c>
+      <c r="K5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>103</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1001</v>
+      </c>
+      <c r="H6" s="5">
+        <v>103</v>
+      </c>
+      <c r="I6" s="5">
+        <v>103</v>
+      </c>
+      <c r="J6" s="5">
+        <v>103</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D10"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
+      <c r="B1" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -735,29 +979,11 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
@@ -765,114 +991,269 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
-        <v>101</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2">
-        <v>101</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1001</v>
-      </c>
-      <c r="I4" s="5">
-        <v>101</v>
-      </c>
-      <c r="J4" s="5">
-        <v>101</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
-        <v>102</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="2">
-        <v>102</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1001</v>
-      </c>
-      <c r="I5" s="5">
-        <v>102</v>
-      </c>
-      <c r="J5" s="5">
-        <v>102</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
-        <v>103</v>
-      </c>
-      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>500</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2">
+        <v>5690</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2">
+        <v>6080</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2">
+        <v>6470</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2">
+        <v>6860</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2">
+        <v>7250</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>21</v>
+      </c>
+      <c r="C24" s="2">
+        <v>7640</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2">
+        <v>8030</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2">
+        <v>8420</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>24</v>
+      </c>
+      <c r="C27" s="2">
+        <v>8810</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>25</v>
+      </c>
+      <c r="C28" s="2">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
         <v>26</v>
       </c>
-      <c r="D6" s="2">
-        <v>103</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1001</v>
-      </c>
-      <c r="I6" s="5">
-        <v>103</v>
-      </c>
-      <c r="J6" s="5">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E10"/>
+      <c r="C29" s="2">
+        <v>9590</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>27</v>
+      </c>
+      <c r="C30" s="2">
+        <v>9980</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>28</v>
+      </c>
+      <c r="C31" s="2">
+        <v>10370</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>29</v>
+      </c>
+      <c r="C32" s="2">
+        <v>10760</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="2">
+        <v>30</v>
+      </c>
+      <c r="C33" s="2">
+        <v>11150</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Character" sheetId="7" r:id="rId2"/>
     <sheet name="#LevelExp" sheetId="9" r:id="rId3"/>
+    <sheet name="#UnlockCondition" sheetId="10" r:id="rId4"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -32,10 +33,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -57,23 +58,19 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CharacterTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -89,11 +86,11 @@
       </rPr>
       <t>ID</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CharacterTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -110,7 +107,7 @@
       </rPr>
       <t>ath</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -127,99 +124,298 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Hero_01</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>기사</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>광전사</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>마검사</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class_Ranged</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class_Mage</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CharacterType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class1_SkillSet</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class1_ReqLv</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class2_ReqLv</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Class2_SkillSet</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>LevelupStatID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>BaseSkillSet</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>LevelExp</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>TotalExperience</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Free</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterUnlockState</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockConditionID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CharacterUnlockState</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Free</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공짜</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>재화 소모</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyCost_1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyCost_2</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Melee</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Ranged</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knight</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Berserker</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arc Knight</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dragon Knight</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Force Blader</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rune Blader</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleCharacter_01_s</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SampleCharacter_03</t>
+  </si>
+  <si>
+    <t>SampleCharacter_Play_Monster_1</t>
+  </si>
+  <si>
+    <t>!CharacterTypes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterGrade</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Star_01</t>
+  </si>
+  <si>
+    <t>Star_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Star_02</t>
+  </si>
+  <si>
+    <t>Star_03</t>
+  </si>
+  <si>
+    <t>Star_04</t>
+  </si>
+  <si>
+    <t>Star_05</t>
+  </si>
+  <si>
+    <t>Grade</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CharacterGrade</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockCondition</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockState</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -369,15 +565,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -391,29 +587,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -691,7 +893,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -699,7 +901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -715,33 +917,84 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
@@ -749,19 +1002,22 @@
     <col min="3" max="3" width="21.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="31.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -769,13 +1025,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
@@ -783,41 +1039,50 @@
       <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
+      <c r="J2" s="11" t="s">
+        <v>36</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -825,120 +1090,261 @@
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>31</v>
+      <c r="J3" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="5">
+        <v>59</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5">
         <v>1001</v>
       </c>
-      <c r="H4" s="5">
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
         <v>101</v>
       </c>
-      <c r="I4" s="5">
+      <c r="L4" s="5">
         <v>101</v>
       </c>
-      <c r="J4" s="5">
+      <c r="M4" s="5">
         <v>101</v>
       </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N4" s="5"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="5">
+        <v>61</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="5">
         <v>1001</v>
       </c>
-      <c r="H5" s="5">
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
         <v>102</v>
       </c>
-      <c r="I5" s="5">
+      <c r="L5" s="5">
         <v>102</v>
       </c>
-      <c r="J5" s="5">
+      <c r="M5" s="5">
         <v>102</v>
       </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="5">
+        <v>60</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="5">
         <v>1001</v>
       </c>
-      <c r="H6" s="5">
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
         <v>103</v>
       </c>
-      <c r="I6" s="5">
+      <c r="L6" s="5">
         <v>103</v>
       </c>
-      <c r="J6" s="5">
+      <c r="M6" s="5">
         <v>103</v>
       </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N6" s="5"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>201</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1001</v>
+      </c>
+      <c r="J7" s="5">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5">
+        <v>103</v>
+      </c>
+      <c r="L7" s="5">
+        <v>103</v>
+      </c>
+      <c r="M7" s="5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>202</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1001</v>
+      </c>
+      <c r="J8" s="5">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5">
+        <v>103</v>
+      </c>
+      <c r="L8" s="5">
+        <v>103</v>
+      </c>
+      <c r="M8" s="5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>203</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1001</v>
+      </c>
+      <c r="J9" s="5">
+        <v>2</v>
+      </c>
+      <c r="K9" s="5">
+        <v>103</v>
+      </c>
+      <c r="L9" s="5">
+        <v>103</v>
+      </c>
+      <c r="M9" s="5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -970,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -979,7 +1385,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="12"/>
@@ -991,7 +1397,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="12"/>
@@ -1253,7 +1659,126 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="17.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2000</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="3"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
     <sheet name="#Character" sheetId="7" r:id="rId2"/>
     <sheet name="#LevelExp" sheetId="9" r:id="rId3"/>
     <sheet name="#UnlockCondition" sheetId="10" r:id="rId4"/>
+    <sheet name="#LevelupCost" sheetId="12" r:id="rId5"/>
+    <sheet name="#CharacterTrait" sheetId="13" r:id="rId6"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -33,10 +35,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="108">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -58,19 +60,19 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -86,11 +88,7 @@
       </rPr>
       <t>ID</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -107,7 +105,7 @@
       </rPr>
       <t>ath</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -124,175 +122,147 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Hero_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Ranged</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Melee</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelupStatID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelExp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalExperience</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Free</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterUnlockState</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockConditionID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CharacterUnlockState</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Free</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공짜</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>재화 소모</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyCost_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyCost_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Class_Ranged</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Mage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class1_SkillSet</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Melee</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class1_ReqLv</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class2_ReqLv</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class2_SkillSet</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelupStatID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseSkillSet</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelExp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>TotalExperience</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Free</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterUnlockState</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Currency</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>UnlockConditionID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CharacterUnlockState</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Free</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>공짜</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>재화 소모</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyType_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyCost_1</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyType_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyCost_2</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dia</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Melee</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Mage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Class_Ranged</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Knight</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Berserker</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Arc Knight</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Dragon Knight</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Force Blader</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Rune Blader</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -309,7 +279,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -326,11 +296,11 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SampleCharacter_01_s</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>SampleCharacter_03</t>
@@ -340,18 +310,18 @@
   </si>
   <si>
     <t>!CharacterTypes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CharacterGrade</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Star_01</t>
   </si>
   <si>
     <t>Star_01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Star_02</t>
@@ -367,31 +337,241 @@
   </si>
   <si>
     <t>Grade</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!CharacterGrade</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>UnlockCondition</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>UnlockState</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterTypes</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Class_Melee</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialID_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aterialValue_01</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelupCost</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialID_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialValue_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyValue_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyValue_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>old</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitGroup_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitGroup_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitGroup_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitGroup_5</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqLv</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Character</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Trait</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+  </si>
+  <si>
+    <t>SkillID_4</t>
+  </si>
+  <si>
+    <t>SkillID_5</t>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Attack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Attack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitGroup_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -565,15 +745,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -587,35 +767,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -917,22 +1103,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -940,17 +1126,17 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -958,36 +1144,36 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1008,12 +1194,9 @@
     <col min="9" max="9" width="8.125" style="2" customWidth="1"/>
     <col min="10" max="10" width="16.625" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="12.75" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1031,7 +1214,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
@@ -1040,40 +1223,40 @@
         <v>5</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -1082,7 +1265,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -1091,28 +1274,28 @@
         <v>6</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>7</v>
@@ -1132,19 +1315,19 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="G4" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="5">
         <v>1001</v>
@@ -1158,29 +1341,40 @@
       <c r="L4" s="5">
         <v>101</v>
       </c>
-      <c r="M4" s="5">
-        <v>101</v>
-      </c>
-      <c r="N4" s="5"/>
+      <c r="M4" s="2">
+        <v>1001</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1002</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1004</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>1005</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" s="5">
         <v>1001</v>
@@ -1195,28 +1389,39 @@
         <v>102</v>
       </c>
       <c r="M5" s="5">
-        <v>102</v>
-      </c>
-      <c r="N5" s="5"/>
+        <v>2001</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2002</v>
+      </c>
+      <c r="O5" s="5">
+        <v>2003</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2004</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>2005</v>
+      </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I6" s="5">
         <v>1001</v>
@@ -1231,28 +1436,39 @@
         <v>103</v>
       </c>
       <c r="M6" s="5">
-        <v>103</v>
-      </c>
-      <c r="N6" s="5"/>
+        <v>3001</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3002</v>
+      </c>
+      <c r="O6" s="5">
+        <v>3003</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3004</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>3005</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" s="5">
         <v>1001</v>
@@ -1266,8 +1482,20 @@
       <c r="L7" s="5">
         <v>103</v>
       </c>
-      <c r="M7" s="5">
-        <v>103</v>
+      <c r="M7" s="2">
+        <v>4001</v>
+      </c>
+      <c r="N7" s="2">
+        <v>4002</v>
+      </c>
+      <c r="O7" s="2">
+        <v>4003</v>
+      </c>
+      <c r="P7" s="2">
+        <v>4004</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>4005</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -1275,19 +1503,19 @@
         <v>202</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8" s="5">
         <v>1001</v>
@@ -1302,7 +1530,19 @@
         <v>103</v>
       </c>
       <c r="M8" s="5">
-        <v>103</v>
+        <v>5001</v>
+      </c>
+      <c r="N8" s="5">
+        <v>5002</v>
+      </c>
+      <c r="O8" s="5">
+        <v>5003</v>
+      </c>
+      <c r="P8" s="5">
+        <v>5004</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>5005</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1310,19 +1550,19 @@
         <v>203</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I9" s="5">
         <v>1001</v>
@@ -1337,14 +1577,26 @@
         <v>103</v>
       </c>
       <c r="M9" s="5">
-        <v>103</v>
+        <v>6001</v>
+      </c>
+      <c r="N9" s="5">
+        <v>6002</v>
+      </c>
+      <c r="O9" s="5">
+        <v>6003</v>
+      </c>
+      <c r="P9" s="5">
+        <v>6004</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>6005</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="D10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1352,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
@@ -1376,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1385,7 +1637,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="12"/>
@@ -1397,7 +1649,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="12"/>
@@ -1421,7 +1673,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="2">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -1434,7 +1686,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="2">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -1447,7 +1699,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2">
-        <v>1000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1455,7 +1707,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="2">
-        <v>1500</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1463,7 +1715,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="2">
-        <v>1790</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1471,7 +1723,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="2">
-        <v>2180</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1479,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="2">
-        <v>2570</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1487,7 +1739,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="2">
-        <v>2960</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1495,7 +1747,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="2">
-        <v>3350</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1503,7 +1755,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="2">
-        <v>3740</v>
+        <v>8350</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1511,7 +1763,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2">
-        <v>4130</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1519,7 +1771,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="2">
-        <v>4520</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
@@ -1527,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="2">
-        <v>4910</v>
+        <v>10900</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -1535,7 +1787,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="2">
-        <v>5300</v>
+        <v>11750</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
@@ -1543,7 +1795,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="2">
-        <v>5690</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
@@ -1551,7 +1803,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>6080</v>
+        <v>13450</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -1559,7 +1811,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="2">
-        <v>6470</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
@@ -1567,7 +1819,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="2">
-        <v>6860</v>
+        <v>15150</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
@@ -1575,7 +1827,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="2">
-        <v>7250</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.3">
@@ -1583,7 +1835,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="2">
-        <v>7640</v>
+        <v>16850</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
@@ -1591,7 +1843,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="2">
-        <v>8030</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
@@ -1599,7 +1851,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="2">
-        <v>8420</v>
+        <v>18550</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
@@ -1607,7 +1859,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="2">
-        <v>8810</v>
+        <v>19400</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
@@ -1615,7 +1867,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="2">
-        <v>9200</v>
+        <v>20250</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
@@ -1623,7 +1875,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="2">
-        <v>9590</v>
+        <v>21100</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
@@ -1631,7 +1883,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="2">
-        <v>9980</v>
+        <v>21950</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
@@ -1639,7 +1891,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="2">
-        <v>10370</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
@@ -1647,7 +1899,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="2">
-        <v>10760</v>
+        <v>23650</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -1655,11 +1907,571 @@
         <v>30</v>
       </c>
       <c r="C33" s="2">
-        <v>11150</v>
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
+        <v>31</v>
+      </c>
+      <c r="C34" s="2">
+        <v>25350</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="2">
+        <v>32</v>
+      </c>
+      <c r="C35" s="2">
+        <v>26200</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <v>33</v>
+      </c>
+      <c r="C36" s="2">
+        <v>27050</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B37" s="2">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2">
+        <v>27900</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="2">
+        <v>35</v>
+      </c>
+      <c r="C38" s="2">
+        <v>28750</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B39" s="2">
+        <v>36</v>
+      </c>
+      <c r="C39" s="2">
+        <v>29600</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B40" s="2">
+        <v>37</v>
+      </c>
+      <c r="C40" s="2">
+        <v>30450</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
+        <v>38</v>
+      </c>
+      <c r="C41" s="2">
+        <v>31300</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="2">
+        <v>39</v>
+      </c>
+      <c r="C42" s="2">
+        <v>32150</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B43" s="2">
+        <v>40</v>
+      </c>
+      <c r="C43" s="2">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
+        <v>41</v>
+      </c>
+      <c r="C44" s="2">
+        <v>33850</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B45" s="2">
+        <v>42</v>
+      </c>
+      <c r="C45" s="2">
+        <v>34700</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <v>43</v>
+      </c>
+      <c r="C46" s="2">
+        <v>35550</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B47" s="2">
+        <v>44</v>
+      </c>
+      <c r="C47" s="2">
+        <v>36400</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="2">
+        <v>45</v>
+      </c>
+      <c r="C48" s="2">
+        <v>37250</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="2">
+        <v>46</v>
+      </c>
+      <c r="C49" s="2">
+        <v>38100</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" s="2">
+        <v>47</v>
+      </c>
+      <c r="C50" s="2">
+        <v>38950</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="2">
+        <v>48</v>
+      </c>
+      <c r="C51" s="2">
+        <v>39800</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <v>49</v>
+      </c>
+      <c r="C52" s="2">
+        <v>40650</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B53" s="2">
+        <v>50</v>
+      </c>
+      <c r="C53" s="2">
+        <v>41500</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B54" s="2">
+        <v>51</v>
+      </c>
+      <c r="C54" s="2">
+        <v>42350</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B55" s="2">
+        <v>52</v>
+      </c>
+      <c r="C55" s="2">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B56" s="2">
+        <v>53</v>
+      </c>
+      <c r="C56" s="2">
+        <v>44050</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B57" s="2">
+        <v>54</v>
+      </c>
+      <c r="C57" s="2">
+        <v>44900</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B58" s="2">
+        <v>55</v>
+      </c>
+      <c r="C58" s="2">
+        <v>45750</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B59" s="2">
+        <v>56</v>
+      </c>
+      <c r="C59" s="2">
+        <v>46600</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B60" s="2">
+        <v>57</v>
+      </c>
+      <c r="C60" s="2">
+        <v>47450</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B61" s="2">
+        <v>58</v>
+      </c>
+      <c r="C61" s="2">
+        <v>48300</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B62" s="2">
+        <v>59</v>
+      </c>
+      <c r="C62" s="2">
+        <v>49150</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B63" s="2">
+        <v>60</v>
+      </c>
+      <c r="C63" s="2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B64" s="2">
+        <v>61</v>
+      </c>
+      <c r="C64" s="2">
+        <v>50850</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B65" s="2">
+        <v>62</v>
+      </c>
+      <c r="C65" s="2">
+        <v>51700</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B66" s="2">
+        <v>63</v>
+      </c>
+      <c r="C66" s="2">
+        <v>52550</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B67" s="2">
+        <v>64</v>
+      </c>
+      <c r="C67" s="2">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B68" s="2">
+        <v>65</v>
+      </c>
+      <c r="C68" s="2">
+        <v>54250</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B69" s="2">
+        <v>66</v>
+      </c>
+      <c r="C69" s="2">
+        <v>55100</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B70" s="2">
+        <v>67</v>
+      </c>
+      <c r="C70" s="2">
+        <v>55950</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B71" s="2">
+        <v>68</v>
+      </c>
+      <c r="C71" s="2">
+        <v>56800</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B72" s="2">
+        <v>69</v>
+      </c>
+      <c r="C72" s="2">
+        <v>57650</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B73" s="2">
+        <v>70</v>
+      </c>
+      <c r="C73" s="2">
+        <v>58500</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B74" s="2">
+        <v>71</v>
+      </c>
+      <c r="C74" s="2">
+        <v>59350</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B75" s="2">
+        <v>72</v>
+      </c>
+      <c r="C75" s="2">
+        <v>60200</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B76" s="2">
+        <v>73</v>
+      </c>
+      <c r="C76" s="2">
+        <v>61050</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B77" s="2">
+        <v>74</v>
+      </c>
+      <c r="C77" s="2">
+        <v>61900</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B78" s="2">
+        <v>75</v>
+      </c>
+      <c r="C78" s="2">
+        <v>62750</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B79" s="2">
+        <v>76</v>
+      </c>
+      <c r="C79" s="2">
+        <v>63600</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B80" s="2">
+        <v>77</v>
+      </c>
+      <c r="C80" s="2">
+        <v>64450</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B81" s="2">
+        <v>78</v>
+      </c>
+      <c r="C81" s="2">
+        <v>65300</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B82" s="2">
+        <v>79</v>
+      </c>
+      <c r="C82" s="2">
+        <v>66150</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B83" s="2">
+        <v>80</v>
+      </c>
+      <c r="C83" s="2">
+        <v>67000</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B84" s="2">
+        <v>81</v>
+      </c>
+      <c r="C84" s="2">
+        <v>67850</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B85" s="2">
+        <v>82</v>
+      </c>
+      <c r="C85" s="2">
+        <v>68700</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B86" s="2">
+        <v>83</v>
+      </c>
+      <c r="C86" s="2">
+        <v>69550</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B87" s="2">
+        <v>84</v>
+      </c>
+      <c r="C87" s="2">
+        <v>70400</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B88" s="2">
+        <v>85</v>
+      </c>
+      <c r="C88" s="2">
+        <v>71250</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B89" s="2">
+        <v>86</v>
+      </c>
+      <c r="C89" s="2">
+        <v>72100</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B90" s="2">
+        <v>87</v>
+      </c>
+      <c r="C90" s="2">
+        <v>72950</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B91" s="2">
+        <v>88</v>
+      </c>
+      <c r="C91" s="2">
+        <v>73800</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B92" s="2">
+        <v>89</v>
+      </c>
+      <c r="C92" s="2">
+        <v>74650</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B93" s="2">
+        <v>90</v>
+      </c>
+      <c r="C93" s="2">
+        <v>75500</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B94" s="2">
+        <v>91</v>
+      </c>
+      <c r="C94" s="2">
+        <v>76350</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B95" s="2">
+        <v>92</v>
+      </c>
+      <c r="C95" s="2">
+        <v>77200</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B96" s="2">
+        <v>93</v>
+      </c>
+      <c r="C96" s="2">
+        <v>78050</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B97" s="2">
+        <v>94</v>
+      </c>
+      <c r="C97" s="2">
+        <v>78900</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B98" s="2">
+        <v>95</v>
+      </c>
+      <c r="C98" s="2">
+        <v>79750</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B99" s="2">
+        <v>96</v>
+      </c>
+      <c r="C99" s="2">
+        <v>80600</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B100" s="2">
+        <v>97</v>
+      </c>
+      <c r="C100" s="2">
+        <v>81450</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B101" s="2">
+        <v>98</v>
+      </c>
+      <c r="C101" s="2">
+        <v>82300</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B102" s="2">
+        <v>99</v>
+      </c>
+      <c r="C102" s="2">
+        <v>83150</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B103" s="2">
+        <v>100</v>
+      </c>
+      <c r="C103" s="2">
+        <v>84000</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1688,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1700,19 +2512,19 @@
         <v>4</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -1724,19 +2536,19 @@
         <v>6</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1744,10 +2556,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -1759,13 +2571,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F5" s="5">
         <v>2000</v>
@@ -1777,8 +2589,1715 @@
       <c r="C9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J103"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="10.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="5">
+        <v>100</v>
+      </c>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="5">
+        <v>300</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="5">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="5">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>9</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="5">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>12</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H15" s="5">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>13</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="5">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>14</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="5">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="5">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>16</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H19" s="5">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>17</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H20" s="5">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>18</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="5">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>19</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" s="5">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>20</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="5">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>21</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H24" s="5">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>22</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="5">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>23</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" s="5">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>24</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="5">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>25</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="5">
+        <v>4700</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>26</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" s="5">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>27</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H30" s="5">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>28</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="5">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>29</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H32" s="5">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2">
+        <v>30</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H33" s="5">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
+        <v>31</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H34" s="5">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="2">
+        <v>32</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" s="5">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <v>33</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="5">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="2">
+        <v>34</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" s="5">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="2">
+        <v>35</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H38" s="5">
+        <v>6700</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="2">
+        <v>36</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H39" s="5">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="2">
+        <v>37</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H40" s="5">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
+        <v>38</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" s="5">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="2">
+        <v>39</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H42" s="5">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="2">
+        <v>40</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H43" s="5">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
+        <v>41</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H44" s="5">
+        <v>7900</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="2">
+        <v>42</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H45" s="5">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <v>43</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H46" s="5">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B47" s="2">
+        <v>44</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H47" s="5">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B48" s="2">
+        <v>45</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H48" s="5">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B49" s="2">
+        <v>46</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H49" s="5">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B50" s="2">
+        <v>47</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H50" s="5">
+        <v>9100</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J50" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B51" s="2">
+        <v>48</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" s="5">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <v>49</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H52" s="5">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B53" s="2">
+        <v>50</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H53" s="5">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B54" s="2">
+        <v>51</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H54" s="5">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B55" s="2">
+        <v>52</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H55" s="5">
+        <v>10100</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B56" s="2">
+        <v>53</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H56" s="5">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B57" s="2">
+        <v>54</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H57" s="5">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B58" s="2">
+        <v>55</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H58" s="5">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B59" s="2">
+        <v>56</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H59" s="5">
+        <v>10900</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B60" s="2">
+        <v>57</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H60" s="5">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B61" s="2">
+        <v>58</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H61" s="5">
+        <v>11300</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B62" s="2">
+        <v>59</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H62" s="5">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B63" s="2">
+        <v>60</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H63" s="5">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B64" s="2">
+        <v>61</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H64" s="5">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B65" s="2">
+        <v>62</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H65" s="5">
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B66" s="2">
+        <v>63</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H66" s="5">
+        <v>12300</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B67" s="2">
+        <v>64</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H67" s="5">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B68" s="2">
+        <v>65</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H68" s="5">
+        <v>12700</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B69" s="2">
+        <v>66</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H69" s="5">
+        <v>12900</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B70" s="2">
+        <v>67</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H70" s="5">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B71" s="2">
+        <v>68</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H71" s="5">
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B72" s="2">
+        <v>69</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H72" s="5">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B73" s="2">
+        <v>70</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H73" s="5">
+        <v>13700</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B74" s="2">
+        <v>71</v>
+      </c>
+      <c r="G74" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H74" s="5">
+        <v>13900</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B75" s="2">
+        <v>72</v>
+      </c>
+      <c r="G75" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H75" s="5">
+        <v>14100</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B76" s="2">
+        <v>73</v>
+      </c>
+      <c r="G76" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H76" s="5">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B77" s="2">
+        <v>74</v>
+      </c>
+      <c r="G77" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H77" s="5">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B78" s="2">
+        <v>75</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H78" s="5">
+        <v>14700</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J78" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B79" s="2">
+        <v>76</v>
+      </c>
+      <c r="G79" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H79" s="5">
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B80" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H80" s="5">
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B81" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H81" s="5">
+        <v>15300</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B82" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H82" s="5">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B83" s="2">
+        <v>80</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H83" s="5">
+        <v>15700</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B84" s="2">
+        <v>81</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H84" s="5">
+        <v>15900</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B85" s="2">
+        <v>82</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H85" s="5">
+        <v>16100</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B86" s="2">
+        <v>83</v>
+      </c>
+      <c r="G86" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H86" s="5">
+        <v>16300</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B87" s="2">
+        <v>84</v>
+      </c>
+      <c r="G87" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H87" s="5">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B88" s="2">
+        <v>85</v>
+      </c>
+      <c r="G88" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H88" s="5">
+        <v>16700</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B89" s="2">
+        <v>86</v>
+      </c>
+      <c r="G89" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H89" s="5">
+        <v>16900</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B90" s="2">
+        <v>87</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H90" s="5">
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B91" s="2">
+        <v>88</v>
+      </c>
+      <c r="G91" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H91" s="5">
+        <v>17300</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B92" s="2">
+        <v>89</v>
+      </c>
+      <c r="G92" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H92" s="5">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B93" s="2">
+        <v>90</v>
+      </c>
+      <c r="G93" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H93" s="5">
+        <v>17700</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B94" s="2">
+        <v>91</v>
+      </c>
+      <c r="G94" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H94" s="5">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B95" s="2">
+        <v>92</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H95" s="5">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B96" s="2">
+        <v>93</v>
+      </c>
+      <c r="G96" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H96" s="5">
+        <v>18300</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B97" s="2">
+        <v>94</v>
+      </c>
+      <c r="G97" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H97" s="5">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B98" s="2">
+        <v>95</v>
+      </c>
+      <c r="G98" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H98" s="5">
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B99" s="2">
+        <v>96</v>
+      </c>
+      <c r="G99" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H99" s="5">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B100" s="2">
+        <v>97</v>
+      </c>
+      <c r="G100" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H100" s="5">
+        <v>19100</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B101" s="2">
+        <v>98</v>
+      </c>
+      <c r="G101" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H101" s="5">
+        <v>19300</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B102" s="2">
+        <v>99</v>
+      </c>
+      <c r="G102" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H102" s="5">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B103" s="2">
+        <v>100</v>
+      </c>
+      <c r="G103" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H103" s="5">
+        <v>19700</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J103" s="2">
+        <v>25000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="3" width="9" style="2"/>
+    <col min="4" max="5" width="21.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="24.5" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="25.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>1002</v>
+      </c>
+      <c r="C5" s="2">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C6" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>1004</v>
+      </c>
+      <c r="C7" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>2002</v>
+      </c>
+      <c r="C10" s="2">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>2003</v>
+      </c>
+      <c r="C11" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>2004</v>
+      </c>
+      <c r="C12" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>2005</v>
+      </c>
+      <c r="C13" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>3001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>3002</v>
+      </c>
+      <c r="C15" s="2">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>3003</v>
+      </c>
+      <c r="C16" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>3004</v>
+      </c>
+      <c r="C17" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>3005</v>
+      </c>
+      <c r="C18" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>4001</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>4002</v>
+      </c>
+      <c r="C20" s="2">
+        <v>25</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>4003</v>
+      </c>
+      <c r="C21" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>4004</v>
+      </c>
+      <c r="C22" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>4005</v>
+      </c>
+      <c r="C23" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>5001</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>5002</v>
+      </c>
+      <c r="C25" s="2">
+        <v>25</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>5003</v>
+      </c>
+      <c r="C26" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <v>5004</v>
+      </c>
+      <c r="C27" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>5005</v>
+      </c>
+      <c r="C28" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>6001</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>6002</v>
+      </c>
+      <c r="C30" s="2">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>6003</v>
+      </c>
+      <c r="C31" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>6004</v>
+      </c>
+      <c r="C32" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="2">
+        <v>6005</v>
+      </c>
+      <c r="C33" s="2">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -35,10 +35,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="110">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="9" type="noConversion"/>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
@@ -60,19 +60,19 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>BaseStatID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -88,7 +88,7 @@
       </rPr>
       <t>ID</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -105,7 +105,7 @@
       </rPr>
       <t>ath</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -122,147 +122,147 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Hero_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Class_Ranged</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Class_Mage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CharacterType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>LevelupStatID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>LevelExp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TotalExperience</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Free</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CharacterUnlockState</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Currency</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>UnlockConditionID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!CharacterUnlockState</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Free</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>공짜</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>재화 소모</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyCost_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyCost_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Class_Mage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Class_Ranged</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Knight</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Berserker</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Arc Knight</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Dragon Knight</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Force Blader</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Rune Blader</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -279,7 +279,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -296,11 +296,11 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>SampleCharacter_01_s</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>SampleCharacter_03</t>
@@ -310,18 +310,18 @@
   </si>
   <si>
     <t>!CharacterTypes</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CharacterGrade</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Star_01</t>
   </si>
   <si>
     <t>Star_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Star_02</t>
@@ -337,31 +337,31 @@
   </si>
   <si>
     <t>Grade</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!CharacterGrade</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>UnlockCondition</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>UnlockState</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CharacterTypes</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Class_Melee</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MaterialID_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -378,43 +378,43 @@
       </rPr>
       <t>aterialValue_01</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>LevelupCost</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MaterialID_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>MaterialValue_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyValue_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyValue_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -430,62 +430,111 @@
       </rPr>
       <t>old</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TraitGroup_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TraitGroup_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TraitGroup_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>TraitGroup_5</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillID_3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReqLv</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_02</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_03</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_01</t>
+  </si>
+  <si>
+    <t>SKILL_PASSIVE_02</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_POWERATTACK_01</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+  </si>
+  <si>
+    <t>SkillID_4</t>
+  </si>
+  <si>
+    <t>SkillID_5</t>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power Attack</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Attack</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_02</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_03</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!SkillInfo</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_BASEATTACK_01</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TraitGroup_1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>SkillID_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReqLv</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -502,68 +551,35 @@
       </rPr>
       <t>Trait</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-  </si>
-  <si>
-    <t>SkillID_4</t>
-  </si>
-  <si>
-    <t>SkillID_5</t>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Power Attack</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Attack</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>TraitGroup_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -745,15 +761,15 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -767,41 +783,44 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,7 +1098,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1173,7 +1192,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1244,7 +1263,7 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>81</v>
@@ -1596,7 +1615,7 @@
       <c r="D10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2471,7 +2490,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2589,7 +2608,7 @@
       <c r="C9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3814,66 +3833,69 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
-    <col min="4" max="5" width="21.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="4" max="6" width="21.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25.375" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B1" s="18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -3882,28 +3904,31 @@
         <v>76</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
@@ -3911,13 +3936,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1002</v>
       </c>
@@ -3925,25 +3950,25 @@
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
@@ -3951,7 +3976,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
@@ -3959,7 +3984,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
@@ -3967,7 +3992,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>2001</v>
       </c>
@@ -3975,13 +4000,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>2002</v>
       </c>
@@ -3989,25 +4014,25 @@
         <v>25</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>2003</v>
       </c>
@@ -4015,7 +4040,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>2004</v>
       </c>
@@ -4023,7 +4048,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>2005</v>
       </c>
@@ -4031,7 +4056,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>3001</v>
       </c>
@@ -4039,13 +4064,13 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>3002</v>
       </c>
@@ -4053,25 +4078,25 @@
         <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J15" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>3003</v>
       </c>
@@ -4079,7 +4104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>3004</v>
       </c>
@@ -4087,7 +4112,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>3005</v>
       </c>
@@ -4095,7 +4120,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>4001</v>
       </c>
@@ -4103,16 +4128,16 @@
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>4002</v>
       </c>
@@ -4120,25 +4145,25 @@
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>4003</v>
       </c>
@@ -4146,7 +4171,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>4004</v>
       </c>
@@ -4154,7 +4179,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>4005</v>
       </c>
@@ -4162,7 +4187,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>5001</v>
       </c>
@@ -4170,16 +4195,16 @@
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>5002</v>
       </c>
@@ -4187,25 +4212,25 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>5003</v>
       </c>
@@ -4213,7 +4238,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>5004</v>
       </c>
@@ -4221,7 +4246,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>5005</v>
       </c>
@@ -4229,7 +4254,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>6001</v>
       </c>
@@ -4237,16 +4262,16 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>6002</v>
       </c>
@@ -4254,25 +4279,25 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>6003</v>
       </c>
@@ -4280,7 +4305,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>6004</v>
       </c>
@@ -4297,7 +4322,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="124">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -525,15 +525,7 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_BASEATTACK_01</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>TraitGroup_1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_1</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -554,11 +546,64 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Icon</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
+    <t>SkillID_1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cleave</t>
+  </si>
+  <si>
+    <t>Arc Slash</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind Blade</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attacks in a narrow area forward</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attacks in a wide area forward</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attacks in a narrow and long line forward</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV1</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV1</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV5</t>
+  </si>
+  <si>
+    <t>Chance to deal bonus damage on basic attacks</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -769,7 +814,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -822,6 +867,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1098,7 +1146,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1263,7 +1311,7 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>81</v>
@@ -3840,29 +3888,26 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
-    <col min="4" max="6" width="21.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="25.375" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="21.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="45.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -3876,26 +3921,23 @@
       <c r="E2" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>108</v>
+      <c r="F2" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -3909,11 +3951,11 @@
       <c r="E3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>109</v>
+      <c r="F3" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>93</v>
@@ -3924,11 +3966,8 @@
       <c r="J3" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
@@ -3936,13 +3975,28 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1002</v>
       </c>
@@ -3952,23 +4006,26 @@
       <c r="D5" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="E5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
@@ -3976,7 +4033,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
@@ -3984,7 +4041,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
@@ -3992,7 +4049,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>2001</v>
       </c>
@@ -4000,13 +4057,16 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>2002</v>
       </c>
@@ -4016,11 +4076,14 @@
       <c r="D10" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>89</v>
@@ -4028,11 +4091,8 @@
       <c r="J10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>2003</v>
       </c>
@@ -4040,7 +4100,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>2004</v>
       </c>
@@ -4048,7 +4108,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>2005</v>
       </c>
@@ -4056,7 +4116,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>3001</v>
       </c>
@@ -4064,13 +4124,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>3002</v>
       </c>
@@ -4080,11 +4143,14 @@
       <c r="D15" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>89</v>
@@ -4092,11 +4158,8 @@
       <c r="J15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>3003</v>
       </c>
@@ -4104,7 +4167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>3004</v>
       </c>
@@ -4112,7 +4175,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>3005</v>
       </c>
@@ -4120,7 +4183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>4001</v>
       </c>
@@ -4130,14 +4193,14 @@
       <c r="D19" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>4002</v>
       </c>
@@ -4147,11 +4210,14 @@
       <c r="D20" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>89</v>
@@ -4159,11 +4225,8 @@
       <c r="J20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>4003</v>
       </c>
@@ -4171,7 +4234,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>4004</v>
       </c>
@@ -4179,7 +4242,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>4005</v>
       </c>
@@ -4187,7 +4250,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>5001</v>
       </c>
@@ -4197,14 +4260,14 @@
       <c r="D24" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>5002</v>
       </c>
@@ -4214,11 +4277,14 @@
       <c r="D25" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F25" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>89</v>
@@ -4226,11 +4292,8 @@
       <c r="J25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>5003</v>
       </c>
@@ -4238,7 +4301,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>5004</v>
       </c>
@@ -4246,7 +4309,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>5005</v>
       </c>
@@ -4254,7 +4317,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>6001</v>
       </c>
@@ -4264,14 +4327,14 @@
       <c r="D29" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>6002</v>
       </c>
@@ -4281,11 +4344,14 @@
       <c r="D30" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F30" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>89</v>
@@ -4293,11 +4359,8 @@
       <c r="J30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>6003</v>
       </c>
@@ -4305,7 +4368,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>6004</v>
       </c>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="126">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -604,6 +604,14 @@
   </si>
   <si>
     <t>Chance to deal bonus damage on basic attacks</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillGroupID</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3888,18 +3896,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="21.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="45.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="32" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="45.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -3907,7 +3916,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -3916,28 +3925,31 @@
         <v>87</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -3946,16 +3958,16 @@
         <v>76</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>93</v>
@@ -3966,66 +3978,75 @@
       <c r="J3" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5">
+        <v>101</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1002</v>
       </c>
       <c r="C5" s="2">
         <v>25</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5">
+        <v>102</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
@@ -4033,7 +4054,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
@@ -4041,7 +4062,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
@@ -4049,41 +4070,44 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>2001</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="5">
+        <v>101</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>2002</v>
       </c>
       <c r="C10" s="2">
         <v>25</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="5">
+        <v>102</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>89</v>
@@ -4091,8 +4115,11 @@
       <c r="J10" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K10" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>2003</v>
       </c>
@@ -4100,7 +4127,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>2004</v>
       </c>
@@ -4108,7 +4135,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>2005</v>
       </c>
@@ -4116,41 +4143,44 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>3001</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5">
+        <v>101</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>3002</v>
       </c>
       <c r="C15" s="2">
         <v>25</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="5">
+        <v>102</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>89</v>
@@ -4158,8 +4188,11 @@
       <c r="J15" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K15" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>3003</v>
       </c>
@@ -4167,7 +4200,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>3004</v>
       </c>
@@ -4175,7 +4208,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>3005</v>
       </c>
@@ -4183,41 +4216,44 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>4001</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="5">
+        <v>101</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>4002</v>
       </c>
       <c r="C20" s="2">
         <v>25</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="5">
+        <v>102</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>89</v>
@@ -4225,8 +4261,11 @@
       <c r="J20" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K20" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>4003</v>
       </c>
@@ -4234,7 +4273,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>4004</v>
       </c>
@@ -4242,7 +4281,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>4005</v>
       </c>
@@ -4250,41 +4289,44 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>5001</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="5">
+        <v>101</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>5002</v>
       </c>
       <c r="C25" s="2">
         <v>25</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="5">
+        <v>102</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>89</v>
@@ -4292,8 +4334,11 @@
       <c r="J25" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K25" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>5003</v>
       </c>
@@ -4301,7 +4346,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>5004</v>
       </c>
@@ -4309,7 +4354,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>5005</v>
       </c>
@@ -4317,41 +4362,44 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>6001</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5">
+        <v>101</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>6002</v>
       </c>
       <c r="C30" s="2">
         <v>25</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="5">
+        <v>102</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>89</v>
@@ -4359,8 +4407,11 @@
       <c r="J30" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="K30" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>6003</v>
       </c>
@@ -4368,7 +4419,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>6004</v>
       </c>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="124">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -529,6 +529,67 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
+    <t>SkillID_1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cleave</t>
+  </si>
+  <si>
+    <t>Arc Slash</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind Blade</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attacks in a narrow area forward</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attacks in a wide area forward</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attacks in a narrow and long line forward</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV1</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT1_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV1</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT2_LV5</t>
+  </si>
+  <si>
+    <t>Chance to deal bonus damage on basic attacks</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>Character</t>
     </r>
@@ -543,75 +604,6 @@
       </rPr>
       <t>Trait</t>
     </r>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillID_1</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cleave</t>
-  </si>
-  <si>
-    <t>Arc Slash</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wind Blade</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attacks in a narrow area forward</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attacks in a wide area forward</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attacks in a narrow and long line forward</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV1</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV2</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV3</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV4</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT1_LV5</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV1</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV2</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV3</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV4</t>
-  </si>
-  <si>
-    <t>SKILL_HERO_01_SLOT2_LV5</t>
-  </si>
-  <si>
-    <t>Chance to deal bonus damage on basic attacks</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillGroupID</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -873,11 +865,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1154,7 +1146,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3896,27 +3888,26 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
-    <col min="4" max="4" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="45.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="32" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="21.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="45.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B1" s="19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -3925,31 +3916,28 @@
         <v>87</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="11" t="s">
         <v>97</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -3958,16 +3946,16 @@
         <v>76</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>98</v>
+      <c r="F3" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>93</v>
@@ -3978,25 +3966,22 @@
       <c r="J3" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" s="5">
-        <v>101</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>110</v>
+      <c r="D4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>113</v>
@@ -4010,25 +3995,22 @@
       <c r="J4" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1002</v>
       </c>
       <c r="C5" s="2">
         <v>25</v>
       </c>
-      <c r="D5" s="5">
-        <v>102</v>
+      <c r="D5" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>118</v>
@@ -4042,11 +4024,8 @@
       <c r="J5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
@@ -4054,7 +4033,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
@@ -4062,7 +4041,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
@@ -4070,44 +4049,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>2001</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>2002</v>
       </c>
       <c r="C10" s="2">
         <v>25</v>
       </c>
-      <c r="D10" s="5">
-        <v>102</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>89</v>
@@ -4115,11 +4091,8 @@
       <c r="J10" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>2003</v>
       </c>
@@ -4127,7 +4100,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>2004</v>
       </c>
@@ -4135,7 +4108,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>2005</v>
       </c>
@@ -4143,44 +4116,53 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>3001</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
-      <c r="D14" s="5">
-        <v>101</v>
+      <c r="D14" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>3002</v>
       </c>
       <c r="C15" s="2">
         <v>25</v>
       </c>
-      <c r="D15" s="5">
-        <v>102</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>89</v>
@@ -4188,11 +4170,8 @@
       <c r="J15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>3003</v>
       </c>
@@ -4200,7 +4179,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>3004</v>
       </c>
@@ -4208,7 +4187,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>3005</v>
       </c>
@@ -4216,44 +4195,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>4001</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
       </c>
-      <c r="D19" s="5">
-        <v>101</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="F19" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>4002</v>
       </c>
       <c r="C20" s="2">
         <v>25</v>
       </c>
-      <c r="D20" s="5">
-        <v>102</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>89</v>
@@ -4261,11 +4237,8 @@
       <c r="J20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>4003</v>
       </c>
@@ -4273,7 +4246,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>4004</v>
       </c>
@@ -4281,7 +4254,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>4005</v>
       </c>
@@ -4289,44 +4262,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>5001</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
       </c>
-      <c r="D24" s="5">
-        <v>101</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="F24" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>5002</v>
       </c>
       <c r="C25" s="2">
         <v>25</v>
       </c>
-      <c r="D25" s="5">
-        <v>102</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F25" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>89</v>
@@ -4334,11 +4304,8 @@
       <c r="J25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>5003</v>
       </c>
@@ -4346,7 +4313,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>5004</v>
       </c>
@@ -4354,7 +4321,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>5005</v>
       </c>
@@ -4362,44 +4329,41 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>6001</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
       </c>
-      <c r="D29" s="5">
-        <v>101</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>6002</v>
       </c>
       <c r="C30" s="2">
         <v>25</v>
       </c>
-      <c r="D30" s="5">
-        <v>102</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F30" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>89</v>
@@ -4407,11 +4371,8 @@
       <c r="J30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>6003</v>
       </c>
@@ -4419,7 +4380,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>6004</v>
       </c>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -241,10 +241,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Knight</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>Berserker</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -254,10 +250,6 @@
   </si>
   <si>
     <t>Dragon Knight</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Force Blader</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -465,25 +457,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_POWERATTACK_02</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_03</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_POWERATTACK_01</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>!SkillInfo</t>
   </si>
   <si>
@@ -505,22 +478,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Power Attack</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Attack</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_02</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>SKILL_BASEATTACK_03</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>!SkillInfo</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -533,29 +490,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Cleave</t>
-  </si>
-  <si>
-    <t>Arc Slash</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wind Blade</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attacks in a narrow area forward</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attacks in a wide area forward</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attacks in a narrow and long line forward</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>SKILL_HERO_01_SLOT1_LV1</t>
   </si>
   <si>
@@ -584,10 +518,6 @@
   </si>
   <si>
     <t>SKILL_HERO_01_SLOT2_LV5</t>
-  </si>
-  <si>
-    <t>Chance to deal bonus damage on basic attacks</t>
-    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -604,6 +534,102 @@
       </rPr>
       <t>Trait</t>
     </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스 블레이드</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방 부채꼴 범위의 적에게 데미지를 입힌다</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>포스 필드</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜드 포스 버스터</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터 주변의 공간을 지배하여 자신을 강화하고 적을 약화시킨다</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 시 확률로 전방 일직선 범위의 모든 적에게 강력한 데미지를 입힌다</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이드 슬래시</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>윈드 러너</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터의 공격 속도와 이동 속도를 증가시킨다</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT3_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT4_LV5</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV2</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV3</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV4</t>
+  </si>
+  <si>
+    <t>SKILL_HERO_01_SLOT5_LV5</t>
+  </si>
+  <si>
+    <t>공격 시 확률로 포스를 증폭시켜 적에게 추가 데미지를 입힌다</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Force Blader</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knight</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1146,7 +1172,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1170,12 +1196,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1211,32 +1237,32 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1290,10 +1316,10 @@
         <v>5</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>12</v>
@@ -1311,19 +1337,19 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -1332,7 +1358,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -1341,10 +1367,10 @@
         <v>6</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>13</v>
@@ -1385,13 +1411,13 @@
         <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
@@ -1432,13 +1458,13 @@
         <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>14</v>
@@ -1455,20 +1481,20 @@
       <c r="L5" s="5">
         <v>102</v>
       </c>
-      <c r="M5" s="5">
-        <v>2001</v>
-      </c>
-      <c r="N5" s="5">
-        <v>2002</v>
-      </c>
-      <c r="O5" s="5">
-        <v>2003</v>
-      </c>
-      <c r="P5" s="5">
-        <v>2004</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>2005</v>
+      <c r="M5" s="2">
+        <v>1001</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1002</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1003</v>
+      </c>
+      <c r="P5" s="2">
+        <v>1004</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>1005</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -1479,13 +1505,13 @@
         <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
@@ -1502,20 +1528,20 @@
       <c r="L6" s="5">
         <v>103</v>
       </c>
-      <c r="M6" s="5">
-        <v>3001</v>
-      </c>
-      <c r="N6" s="5">
-        <v>3002</v>
-      </c>
-      <c r="O6" s="5">
-        <v>3003</v>
-      </c>
-      <c r="P6" s="5">
-        <v>3004</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>3005</v>
+      <c r="M6" s="2">
+        <v>1001</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1002</v>
+      </c>
+      <c r="O6" s="2">
+        <v>1003</v>
+      </c>
+      <c r="P6" s="2">
+        <v>1004</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>1005</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1526,13 +1552,13 @@
         <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>14</v>
@@ -1550,19 +1576,19 @@
         <v>103</v>
       </c>
       <c r="M7" s="2">
-        <v>4001</v>
+        <v>1001</v>
       </c>
       <c r="N7" s="2">
-        <v>4002</v>
+        <v>1002</v>
       </c>
       <c r="O7" s="2">
-        <v>4003</v>
+        <v>1003</v>
       </c>
       <c r="P7" s="2">
-        <v>4004</v>
+        <v>1004</v>
       </c>
       <c r="Q7" s="2">
-        <v>4005</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -1573,13 +1599,13 @@
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -1596,20 +1622,20 @@
       <c r="L8" s="5">
         <v>103</v>
       </c>
-      <c r="M8" s="5">
-        <v>5001</v>
-      </c>
-      <c r="N8" s="5">
-        <v>5002</v>
-      </c>
-      <c r="O8" s="5">
-        <v>5003</v>
-      </c>
-      <c r="P8" s="5">
-        <v>5004</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>5005</v>
+      <c r="M8" s="2">
+        <v>1001</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1002</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1003</v>
+      </c>
+      <c r="P8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>1005</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1620,13 +1646,13 @@
         <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>14</v>
@@ -1643,20 +1669,20 @@
       <c r="L9" s="5">
         <v>103</v>
       </c>
-      <c r="M9" s="5">
-        <v>6001</v>
-      </c>
-      <c r="N9" s="5">
-        <v>6002</v>
-      </c>
-      <c r="O9" s="5">
-        <v>6003</v>
-      </c>
-      <c r="P9" s="5">
-        <v>6004</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>6005</v>
+      <c r="M9" s="2">
+        <v>1001</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1002</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1003</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1004</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1005</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -2567,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2579,7 +2605,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
@@ -2688,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2697,28 +2723,28 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="H2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2739,16 +2765,16 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2767,7 +2793,7 @@
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H5" s="5">
         <v>100</v>
@@ -2781,7 +2807,7 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5">
         <v>300</v>
@@ -2794,7 +2820,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H7" s="5">
         <v>500</v>
@@ -2805,7 +2831,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H8" s="5">
         <v>700</v>
@@ -2816,7 +2842,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H9" s="5">
         <v>900</v>
@@ -2827,7 +2853,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H10" s="5">
         <v>1100</v>
@@ -2838,7 +2864,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H11" s="5">
         <v>1300</v>
@@ -2849,7 +2875,7 @@
         <v>9</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H12" s="5">
         <v>1500</v>
@@ -2860,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H13" s="5">
         <v>1700</v>
@@ -2871,7 +2897,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H14" s="5">
         <v>1900</v>
@@ -2882,7 +2908,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H15" s="5">
         <v>2100</v>
@@ -2893,7 +2919,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H16" s="5">
         <v>2300</v>
@@ -2904,7 +2930,7 @@
         <v>14</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H17" s="5">
         <v>2500</v>
@@ -2915,7 +2941,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H18" s="5">
         <v>2700</v>
@@ -2926,7 +2952,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H19" s="5">
         <v>2900</v>
@@ -2937,7 +2963,7 @@
         <v>17</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H20" s="5">
         <v>3100</v>
@@ -2948,7 +2974,7 @@
         <v>18</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H21" s="5">
         <v>3300</v>
@@ -2959,7 +2985,7 @@
         <v>19</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H22" s="5">
         <v>3500</v>
@@ -2970,7 +2996,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H23" s="5">
         <v>3700</v>
@@ -2981,7 +3007,7 @@
         <v>21</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H24" s="5">
         <v>3900</v>
@@ -2992,7 +3018,7 @@
         <v>22</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H25" s="5">
         <v>4100</v>
@@ -3003,7 +3029,7 @@
         <v>23</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H26" s="5">
         <v>4300</v>
@@ -3014,7 +3040,7 @@
         <v>24</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H27" s="5">
         <v>4500</v>
@@ -3025,13 +3051,13 @@
         <v>25</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H28" s="5">
         <v>4700</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J28" s="2">
         <v>1000</v>
@@ -3042,7 +3068,7 @@
         <v>26</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H29" s="5">
         <v>4900</v>
@@ -3053,7 +3079,7 @@
         <v>27</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H30" s="5">
         <v>5100</v>
@@ -3064,7 +3090,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H31" s="5">
         <v>5300</v>
@@ -3075,7 +3101,7 @@
         <v>29</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H32" s="5">
         <v>5500</v>
@@ -3086,7 +3112,7 @@
         <v>30</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H33" s="5">
         <v>5700</v>
@@ -3097,7 +3123,7 @@
         <v>31</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H34" s="5">
         <v>5900</v>
@@ -3108,7 +3134,7 @@
         <v>32</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H35" s="5">
         <v>6100</v>
@@ -3119,7 +3145,7 @@
         <v>33</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H36" s="5">
         <v>6300</v>
@@ -3130,7 +3156,7 @@
         <v>34</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H37" s="5">
         <v>6500</v>
@@ -3141,7 +3167,7 @@
         <v>35</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H38" s="5">
         <v>6700</v>
@@ -3152,7 +3178,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H39" s="5">
         <v>6900</v>
@@ -3163,7 +3189,7 @@
         <v>37</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H40" s="5">
         <v>7100</v>
@@ -3174,7 +3200,7 @@
         <v>38</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H41" s="5">
         <v>7300</v>
@@ -3185,7 +3211,7 @@
         <v>39</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H42" s="5">
         <v>7500</v>
@@ -3196,7 +3222,7 @@
         <v>40</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H43" s="5">
         <v>7700</v>
@@ -3207,7 +3233,7 @@
         <v>41</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H44" s="5">
         <v>7900</v>
@@ -3218,7 +3244,7 @@
         <v>42</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H45" s="5">
         <v>8100</v>
@@ -3229,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H46" s="5">
         <v>8300</v>
@@ -3240,7 +3266,7 @@
         <v>44</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H47" s="5">
         <v>8500</v>
@@ -3251,7 +3277,7 @@
         <v>45</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H48" s="5">
         <v>8700</v>
@@ -3262,7 +3288,7 @@
         <v>46</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H49" s="5">
         <v>8900</v>
@@ -3273,13 +3299,13 @@
         <v>47</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H50" s="5">
         <v>9100</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J50" s="2">
         <v>3000</v>
@@ -3290,7 +3316,7 @@
         <v>48</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H51" s="5">
         <v>9300</v>
@@ -3301,7 +3327,7 @@
         <v>49</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H52" s="5">
         <v>9500</v>
@@ -3312,7 +3338,7 @@
         <v>50</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H53" s="5">
         <v>9700</v>
@@ -3323,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H54" s="5">
         <v>9900</v>
@@ -3334,7 +3360,7 @@
         <v>52</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H55" s="5">
         <v>10100</v>
@@ -3345,7 +3371,7 @@
         <v>53</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H56" s="5">
         <v>10300</v>
@@ -3356,7 +3382,7 @@
         <v>54</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H57" s="5">
         <v>10500</v>
@@ -3367,7 +3393,7 @@
         <v>55</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H58" s="5">
         <v>10700</v>
@@ -3378,7 +3404,7 @@
         <v>56</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H59" s="5">
         <v>10900</v>
@@ -3389,7 +3415,7 @@
         <v>57</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H60" s="5">
         <v>11100</v>
@@ -3400,7 +3426,7 @@
         <v>58</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H61" s="5">
         <v>11300</v>
@@ -3411,7 +3437,7 @@
         <v>59</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H62" s="5">
         <v>11500</v>
@@ -3422,7 +3448,7 @@
         <v>60</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H63" s="5">
         <v>11700</v>
@@ -3433,7 +3459,7 @@
         <v>61</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H64" s="5">
         <v>11900</v>
@@ -3444,7 +3470,7 @@
         <v>62</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H65" s="5">
         <v>12100</v>
@@ -3455,7 +3481,7 @@
         <v>63</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H66" s="5">
         <v>12300</v>
@@ -3466,7 +3492,7 @@
         <v>64</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H67" s="5">
         <v>12500</v>
@@ -3477,7 +3503,7 @@
         <v>65</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H68" s="5">
         <v>12700</v>
@@ -3488,7 +3514,7 @@
         <v>66</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H69" s="5">
         <v>12900</v>
@@ -3499,7 +3525,7 @@
         <v>67</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H70" s="5">
         <v>13100</v>
@@ -3510,7 +3536,7 @@
         <v>68</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H71" s="5">
         <v>13300</v>
@@ -3521,7 +3547,7 @@
         <v>69</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H72" s="5">
         <v>13500</v>
@@ -3532,7 +3558,7 @@
         <v>70</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H73" s="5">
         <v>13700</v>
@@ -3543,7 +3569,7 @@
         <v>71</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H74" s="5">
         <v>13900</v>
@@ -3554,7 +3580,7 @@
         <v>72</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H75" s="5">
         <v>14100</v>
@@ -3565,7 +3591,7 @@
         <v>73</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H76" s="5">
         <v>14300</v>
@@ -3576,7 +3602,7 @@
         <v>74</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H77" s="5">
         <v>14500</v>
@@ -3587,13 +3613,13 @@
         <v>75</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H78" s="5">
         <v>14700</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J78" s="2">
         <v>10000</v>
@@ -3604,7 +3630,7 @@
         <v>76</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H79" s="5">
         <v>14900</v>
@@ -3615,7 +3641,7 @@
         <v>77</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H80" s="5">
         <v>15100</v>
@@ -3626,7 +3652,7 @@
         <v>78</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H81" s="5">
         <v>15300</v>
@@ -3637,7 +3663,7 @@
         <v>79</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H82" s="5">
         <v>15500</v>
@@ -3648,7 +3674,7 @@
         <v>80</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H83" s="5">
         <v>15700</v>
@@ -3659,7 +3685,7 @@
         <v>81</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H84" s="5">
         <v>15900</v>
@@ -3670,7 +3696,7 @@
         <v>82</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H85" s="5">
         <v>16100</v>
@@ -3681,7 +3707,7 @@
         <v>83</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H86" s="5">
         <v>16300</v>
@@ -3692,7 +3718,7 @@
         <v>84</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H87" s="5">
         <v>16500</v>
@@ -3703,7 +3729,7 @@
         <v>85</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H88" s="5">
         <v>16700</v>
@@ -3714,7 +3740,7 @@
         <v>86</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H89" s="5">
         <v>16900</v>
@@ -3725,7 +3751,7 @@
         <v>87</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H90" s="5">
         <v>17100</v>
@@ -3736,7 +3762,7 @@
         <v>88</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H91" s="5">
         <v>17300</v>
@@ -3747,7 +3773,7 @@
         <v>89</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H92" s="5">
         <v>17500</v>
@@ -3758,7 +3784,7 @@
         <v>90</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H93" s="5">
         <v>17700</v>
@@ -3769,7 +3795,7 @@
         <v>91</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H94" s="5">
         <v>17900</v>
@@ -3780,7 +3806,7 @@
         <v>92</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H95" s="5">
         <v>18100</v>
@@ -3791,7 +3817,7 @@
         <v>93</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H96" s="5">
         <v>18300</v>
@@ -3802,7 +3828,7 @@
         <v>94</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H97" s="5">
         <v>18500</v>
@@ -3813,7 +3839,7 @@
         <v>95</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H98" s="5">
         <v>18700</v>
@@ -3824,7 +3850,7 @@
         <v>96</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H99" s="5">
         <v>18900</v>
@@ -3835,7 +3861,7 @@
         <v>97</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H100" s="5">
         <v>19100</v>
@@ -3846,7 +3872,7 @@
         <v>98</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H101" s="5">
         <v>19300</v>
@@ -3857,7 +3883,7 @@
         <v>99</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H102" s="5">
         <v>19500</v>
@@ -3868,13 +3894,13 @@
         <v>100</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H103" s="5">
         <v>19700</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J103" s="2">
         <v>25000</v>
@@ -3888,13 +3914,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
     <col min="4" max="4" width="21.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="45.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.375" style="2" customWidth="1"/>
     <col min="6" max="10" width="32" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
@@ -3904,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3913,28 +3939,28 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3943,28 +3969,28 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -3975,25 +4001,25 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>109</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -4004,25 +4030,25 @@
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -4032,6 +4058,27 @@
       <c r="C6" s="2">
         <v>50</v>
       </c>
+      <c r="D6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -4040,6 +4087,27 @@
       <c r="C7" s="2">
         <v>75</v>
       </c>
+      <c r="D7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -4048,353 +4116,42 @@
       <c r="C8" s="2">
         <v>100</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
-        <v>2001</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
-        <v>2002</v>
-      </c>
-      <c r="C10" s="2">
-        <v>25</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="2">
-        <v>2003</v>
-      </c>
-      <c r="C11" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="2">
-        <v>2004</v>
-      </c>
-      <c r="C12" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="2">
-        <v>2005</v>
-      </c>
-      <c r="C13" s="2">
-        <v>100</v>
-      </c>
+      <c r="E9" s="18"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="2">
-        <v>3001</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="2">
-        <v>3002</v>
-      </c>
-      <c r="C15" s="2">
-        <v>25</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="2">
-        <v>3003</v>
-      </c>
-      <c r="C16" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="2">
-        <v>3004</v>
-      </c>
-      <c r="C17" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="2">
-        <v>3005</v>
-      </c>
-      <c r="C18" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="2">
-        <v>4001</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="2">
-        <v>4002</v>
-      </c>
-      <c r="C20" s="2">
-        <v>25</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="2">
-        <v>4003</v>
-      </c>
-      <c r="C21" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="2">
-        <v>4004</v>
-      </c>
-      <c r="C22" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="2">
-        <v>4005</v>
-      </c>
-      <c r="C23" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="2">
-        <v>5001</v>
-      </c>
-      <c r="C24" s="2">
-        <v>1</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="2">
-        <v>5002</v>
-      </c>
-      <c r="C25" s="2">
-        <v>25</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="2">
-        <v>5003</v>
-      </c>
-      <c r="C26" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="2">
-        <v>5004</v>
-      </c>
-      <c r="C27" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="2">
-        <v>5005</v>
-      </c>
-      <c r="C28" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="2">
-        <v>6001</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B30" s="2">
-        <v>6002</v>
-      </c>
-      <c r="C30" s="2">
-        <v>25</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="2">
-        <v>6003</v>
-      </c>
-      <c r="C31" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B32" s="2">
-        <v>6004</v>
-      </c>
-      <c r="C32" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B33" s="2">
-        <v>6005</v>
-      </c>
-      <c r="C33" s="2">
-        <v>100</v>
-      </c>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="18"/>
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E24" s="18"/>
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E29" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="136">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -630,6 +630,18 @@
   </si>
   <si>
     <t>Knight</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelStepDesc</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">범위+{1}, 데미지+{2}, </t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -3914,18 +3926,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
     <col min="4" max="4" width="21.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="62.375" style="2" customWidth="1"/>
-    <col min="6" max="10" width="32" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="5" max="6" width="62.375" style="2" customWidth="1"/>
+    <col min="7" max="11" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -3933,7 +3945,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -3947,23 +3959,26 @@
       <c r="E2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -3977,11 +3992,11 @@
       <c r="E3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>86</v>
@@ -3992,8 +4007,11 @@
       <c r="J3" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
@@ -4006,23 +4024,26 @@
       <c r="E4" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1002</v>
       </c>
@@ -4035,23 +4056,23 @@
       <c r="E5" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
@@ -4064,23 +4085,23 @@
       <c r="E6" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
@@ -4093,23 +4114,23 @@
       <c r="E7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
@@ -4122,36 +4143,41 @@
       <c r="E8" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E9" s="18"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F9" s="18"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E14" s="18"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="18"/>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E19" s="18"/>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="18"/>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E24" s="18"/>
-    </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="18"/>
+    </row>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -630,18 +630,6 @@
   </si>
   <si>
     <t>Knight</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelStepDesc</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">범위+{1}, 데미지+{2}, </t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1184,7 +1172,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3926,18 +3914,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
     <col min="4" max="4" width="21.75" style="2" customWidth="1"/>
-    <col min="5" max="6" width="62.375" style="2" customWidth="1"/>
-    <col min="7" max="11" width="32" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="62.375" style="2" customWidth="1"/>
+    <col min="6" max="10" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -3945,7 +3933,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -3959,26 +3947,23 @@
       <c r="E2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>133</v>
+      <c r="F2" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -3992,11 +3977,11 @@
       <c r="E3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>134</v>
+      <c r="F3" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>86</v>
@@ -4007,11 +3992,8 @@
       <c r="J3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
@@ -4024,26 +4006,23 @@
       <c r="E4" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>135</v>
+      <c r="F4" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K4" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1002</v>
       </c>
@@ -4056,23 +4035,23 @@
       <c r="E5" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K5" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
@@ -4085,23 +4064,23 @@
       <c r="E6" s="2" t="s">
         <v>114</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>115</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
@@ -4114,23 +4093,23 @@
       <c r="E7" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="F7" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="K7" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
@@ -4143,41 +4122,36 @@
       <c r="E8" s="2" t="s">
         <v>111</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K8" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-    </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-    </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-    </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="140">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="10" type="noConversion"/>
@@ -631,6 +631,29 @@
   <si>
     <t>Knight</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_014</t>
+  </si>
+  <si>
+    <t>skill_015</t>
+  </si>
+  <si>
+    <t>skill_016</t>
+  </si>
+  <si>
+    <t>skill_017</t>
+  </si>
+  <si>
+    <t>skill_018</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1195,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3914,18 +3937,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="3" width="9" style="2"/>
     <col min="4" max="4" width="21.75" style="2" customWidth="1"/>
     <col min="5" max="5" width="62.375" style="2" customWidth="1"/>
-    <col min="6" max="10" width="32" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="17.625" style="2" customWidth="1"/>
+    <col min="7" max="11" width="32" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -3933,7 +3957,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -3947,23 +3971,26 @@
       <c r="E2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="11" t="s">
         <v>7</v>
@@ -3977,11 +4004,11 @@
       <c r="E3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>86</v>
@@ -3992,8 +4019,11 @@
       <c r="J3" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1001</v>
       </c>
@@ -4006,23 +4036,26 @@
       <c r="E4" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1002</v>
       </c>
@@ -4035,23 +4068,26 @@
       <c r="E5" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>1003</v>
       </c>
@@ -4064,23 +4100,26 @@
       <c r="E6" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>1004</v>
       </c>
@@ -4093,23 +4132,26 @@
       <c r="E7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>1005</v>
       </c>
@@ -4122,36 +4164,44 @@
       <c r="E8" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E9" s="18"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F9" s="18"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E14" s="18"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="18"/>
+    </row>
+    <row r="19" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E19" s="18"/>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="18"/>
+    </row>
+    <row r="24" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E24" s="18"/>
-    </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="18"/>
+    </row>
+    <row r="29" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -241,22 +241,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Berserker</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Arc Knight</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dragon Knight</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rune Blader</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>I</t>
     </r>
@@ -625,14 +609,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>Force Blader</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knight</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -654,6 +630,30 @@
   </si>
   <si>
     <t>skill_018</t>
+  </si>
+  <si>
+    <t>검사</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>궁수</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>총사</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>아크나이트</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>룬블레이더</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이트로드</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1195,7 +1195,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1219,12 +1219,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1260,32 +1260,32 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1339,10 +1339,10 @@
         <v>5</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>12</v>
@@ -1360,19 +1360,19 @@
         <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -1381,7 +1381,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>6</v>
@@ -1390,10 +1390,10 @@
         <v>6</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>13</v>
@@ -1434,13 +1434,13 @@
         <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
@@ -1481,13 +1481,13 @@
         <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>14</v>
@@ -1528,13 +1528,13 @@
         <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
@@ -1575,13 +1575,13 @@
         <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>14</v>
@@ -1622,13 +1622,13 @@
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
@@ -1669,13 +1669,13 @@
         <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>14</v>
@@ -2616,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2628,7 +2628,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
@@ -2737,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2746,28 +2746,28 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="G2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2788,16 +2788,16 @@
         <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H5" s="5">
         <v>100</v>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5">
         <v>300</v>
@@ -2843,7 +2843,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5">
         <v>500</v>
@@ -2854,7 +2854,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5">
         <v>700</v>
@@ -2865,7 +2865,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>900</v>
@@ -2876,7 +2876,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H10" s="5">
         <v>1100</v>
@@ -2887,7 +2887,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H11" s="5">
         <v>1300</v>
@@ -2898,7 +2898,7 @@
         <v>9</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H12" s="5">
         <v>1500</v>
@@ -2909,7 +2909,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H13" s="5">
         <v>1700</v>
@@ -2920,7 +2920,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H14" s="5">
         <v>1900</v>
@@ -2931,7 +2931,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H15" s="5">
         <v>2100</v>
@@ -2942,7 +2942,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H16" s="5">
         <v>2300</v>
@@ -2953,7 +2953,7 @@
         <v>14</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H17" s="5">
         <v>2500</v>
@@ -2964,7 +2964,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H18" s="5">
         <v>2700</v>
@@ -2975,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H19" s="5">
         <v>2900</v>
@@ -2986,7 +2986,7 @@
         <v>17</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H20" s="5">
         <v>3100</v>
@@ -2997,7 +2997,7 @@
         <v>18</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H21" s="5">
         <v>3300</v>
@@ -3008,7 +3008,7 @@
         <v>19</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H22" s="5">
         <v>3500</v>
@@ -3019,7 +3019,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H23" s="5">
         <v>3700</v>
@@ -3030,7 +3030,7 @@
         <v>21</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H24" s="5">
         <v>3900</v>
@@ -3041,7 +3041,7 @@
         <v>22</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H25" s="5">
         <v>4100</v>
@@ -3052,7 +3052,7 @@
         <v>23</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H26" s="5">
         <v>4300</v>
@@ -3063,7 +3063,7 @@
         <v>24</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H27" s="5">
         <v>4500</v>
@@ -3074,13 +3074,13 @@
         <v>25</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H28" s="5">
         <v>4700</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J28" s="2">
         <v>1000</v>
@@ -3091,7 +3091,7 @@
         <v>26</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H29" s="5">
         <v>4900</v>
@@ -3102,7 +3102,7 @@
         <v>27</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H30" s="5">
         <v>5100</v>
@@ -3113,7 +3113,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H31" s="5">
         <v>5300</v>
@@ -3124,7 +3124,7 @@
         <v>29</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H32" s="5">
         <v>5500</v>
@@ -3135,7 +3135,7 @@
         <v>30</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H33" s="5">
         <v>5700</v>
@@ -3146,7 +3146,7 @@
         <v>31</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H34" s="5">
         <v>5900</v>
@@ -3157,7 +3157,7 @@
         <v>32</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H35" s="5">
         <v>6100</v>
@@ -3168,7 +3168,7 @@
         <v>33</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H36" s="5">
         <v>6300</v>
@@ -3179,7 +3179,7 @@
         <v>34</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H37" s="5">
         <v>6500</v>
@@ -3190,7 +3190,7 @@
         <v>35</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H38" s="5">
         <v>6700</v>
@@ -3201,7 +3201,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H39" s="5">
         <v>6900</v>
@@ -3212,7 +3212,7 @@
         <v>37</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H40" s="5">
         <v>7100</v>
@@ -3223,7 +3223,7 @@
         <v>38</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H41" s="5">
         <v>7300</v>
@@ -3234,7 +3234,7 @@
         <v>39</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H42" s="5">
         <v>7500</v>
@@ -3245,7 +3245,7 @@
         <v>40</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H43" s="5">
         <v>7700</v>
@@ -3256,7 +3256,7 @@
         <v>41</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H44" s="5">
         <v>7900</v>
@@ -3267,7 +3267,7 @@
         <v>42</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H45" s="5">
         <v>8100</v>
@@ -3278,7 +3278,7 @@
         <v>43</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H46" s="5">
         <v>8300</v>
@@ -3289,7 +3289,7 @@
         <v>44</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H47" s="5">
         <v>8500</v>
@@ -3300,7 +3300,7 @@
         <v>45</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H48" s="5">
         <v>8700</v>
@@ -3311,7 +3311,7 @@
         <v>46</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H49" s="5">
         <v>8900</v>
@@ -3322,13 +3322,13 @@
         <v>47</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H50" s="5">
         <v>9100</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J50" s="2">
         <v>3000</v>
@@ -3339,7 +3339,7 @@
         <v>48</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H51" s="5">
         <v>9300</v>
@@ -3350,7 +3350,7 @@
         <v>49</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H52" s="5">
         <v>9500</v>
@@ -3361,7 +3361,7 @@
         <v>50</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H53" s="5">
         <v>9700</v>
@@ -3372,7 +3372,7 @@
         <v>51</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H54" s="5">
         <v>9900</v>
@@ -3383,7 +3383,7 @@
         <v>52</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H55" s="5">
         <v>10100</v>
@@ -3394,7 +3394,7 @@
         <v>53</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H56" s="5">
         <v>10300</v>
@@ -3405,7 +3405,7 @@
         <v>54</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H57" s="5">
         <v>10500</v>
@@ -3416,7 +3416,7 @@
         <v>55</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H58" s="5">
         <v>10700</v>
@@ -3427,7 +3427,7 @@
         <v>56</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H59" s="5">
         <v>10900</v>
@@ -3438,7 +3438,7 @@
         <v>57</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H60" s="5">
         <v>11100</v>
@@ -3449,7 +3449,7 @@
         <v>58</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H61" s="5">
         <v>11300</v>
@@ -3460,7 +3460,7 @@
         <v>59</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H62" s="5">
         <v>11500</v>
@@ -3471,7 +3471,7 @@
         <v>60</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H63" s="5">
         <v>11700</v>
@@ -3482,7 +3482,7 @@
         <v>61</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H64" s="5">
         <v>11900</v>
@@ -3493,7 +3493,7 @@
         <v>62</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H65" s="5">
         <v>12100</v>
@@ -3504,7 +3504,7 @@
         <v>63</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H66" s="5">
         <v>12300</v>
@@ -3515,7 +3515,7 @@
         <v>64</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H67" s="5">
         <v>12500</v>
@@ -3526,7 +3526,7 @@
         <v>65</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H68" s="5">
         <v>12700</v>
@@ -3537,7 +3537,7 @@
         <v>66</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H69" s="5">
         <v>12900</v>
@@ -3548,7 +3548,7 @@
         <v>67</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H70" s="5">
         <v>13100</v>
@@ -3559,7 +3559,7 @@
         <v>68</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H71" s="5">
         <v>13300</v>
@@ -3570,7 +3570,7 @@
         <v>69</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H72" s="5">
         <v>13500</v>
@@ -3581,7 +3581,7 @@
         <v>70</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H73" s="5">
         <v>13700</v>
@@ -3592,7 +3592,7 @@
         <v>71</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H74" s="5">
         <v>13900</v>
@@ -3603,7 +3603,7 @@
         <v>72</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H75" s="5">
         <v>14100</v>
@@ -3614,7 +3614,7 @@
         <v>73</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H76" s="5">
         <v>14300</v>
@@ -3625,7 +3625,7 @@
         <v>74</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H77" s="5">
         <v>14500</v>
@@ -3636,13 +3636,13 @@
         <v>75</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H78" s="5">
         <v>14700</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J78" s="2">
         <v>10000</v>
@@ -3653,7 +3653,7 @@
         <v>76</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H79" s="5">
         <v>14900</v>
@@ -3664,7 +3664,7 @@
         <v>77</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H80" s="5">
         <v>15100</v>
@@ -3675,7 +3675,7 @@
         <v>78</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H81" s="5">
         <v>15300</v>
@@ -3686,7 +3686,7 @@
         <v>79</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H82" s="5">
         <v>15500</v>
@@ -3697,7 +3697,7 @@
         <v>80</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H83" s="5">
         <v>15700</v>
@@ -3708,7 +3708,7 @@
         <v>81</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H84" s="5">
         <v>15900</v>
@@ -3719,7 +3719,7 @@
         <v>82</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H85" s="5">
         <v>16100</v>
@@ -3730,7 +3730,7 @@
         <v>83</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H86" s="5">
         <v>16300</v>
@@ -3741,7 +3741,7 @@
         <v>84</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H87" s="5">
         <v>16500</v>
@@ -3752,7 +3752,7 @@
         <v>85</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H88" s="5">
         <v>16700</v>
@@ -3763,7 +3763,7 @@
         <v>86</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H89" s="5">
         <v>16900</v>
@@ -3774,7 +3774,7 @@
         <v>87</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H90" s="5">
         <v>17100</v>
@@ -3785,7 +3785,7 @@
         <v>88</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H91" s="5">
         <v>17300</v>
@@ -3796,7 +3796,7 @@
         <v>89</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H92" s="5">
         <v>17500</v>
@@ -3807,7 +3807,7 @@
         <v>90</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H93" s="5">
         <v>17700</v>
@@ -3818,7 +3818,7 @@
         <v>91</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H94" s="5">
         <v>17900</v>
@@ -3829,7 +3829,7 @@
         <v>92</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H95" s="5">
         <v>18100</v>
@@ -3840,7 +3840,7 @@
         <v>93</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H96" s="5">
         <v>18300</v>
@@ -3851,7 +3851,7 @@
         <v>94</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H97" s="5">
         <v>18500</v>
@@ -3862,7 +3862,7 @@
         <v>95</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H98" s="5">
         <v>18700</v>
@@ -3873,7 +3873,7 @@
         <v>96</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H99" s="5">
         <v>18900</v>
@@ -3884,7 +3884,7 @@
         <v>97</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H100" s="5">
         <v>19100</v>
@@ -3895,7 +3895,7 @@
         <v>98</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H101" s="5">
         <v>19300</v>
@@ -3906,7 +3906,7 @@
         <v>99</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H102" s="5">
         <v>19500</v>
@@ -3917,13 +3917,13 @@
         <v>100</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H103" s="5">
         <v>19700</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J103" s="2">
         <v>25000</v>
@@ -3954,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -3963,31 +3963,31 @@
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>89</v>
-      </c>
       <c r="E2" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="H2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -3996,31 +3996,31 @@
         <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -4031,28 +4031,28 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -4063,28 +4063,28 @@
         <v>25</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>136</v>
-      </c>
       <c r="G5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -4095,28 +4095,28 @@
         <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -4127,28 +4127,28 @@
         <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -4159,28 +4159,28 @@
         <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -537,10 +537,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>캐릭터 주변의 공간을 지배하여 자신을 강화하고 적을 약화시킨다</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>공격 시 확률로 전방 일직선 범위의 모든 적에게 강력한 데미지를 입힌다</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -653,6 +649,10 @@
   </si>
   <si>
     <t>나이트로드</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>캐릭터 주변의 공간을 지배하여 자신을 강화하고 일정 시간마다 적에게 피해를 준다</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -1195,7 +1195,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1434,7 +1434,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>45</v>
@@ -1481,7 +1481,7 @@
         <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>47</v>
@@ -1528,7 +1528,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>46</v>
@@ -1575,7 +1575,7 @@
         <v>40</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>45</v>
@@ -1622,7 +1622,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>47</v>
@@ -1669,7 +1669,7 @@
         <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>46</v>
@@ -3972,7 +3972,7 @@
         <v>86</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>90</v>
@@ -4005,7 +4005,7 @@
         <v>87</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>88</v>
@@ -4031,13 +4031,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>103</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>91</v>
@@ -4066,10 +4066,10 @@
         <v>102</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>96</v>
@@ -4095,28 +4095,28 @@
         <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="H6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -4130,25 +4130,25 @@
         <v>104</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -4162,25 +4162,25 @@
         <v>105</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -580,7 +580,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -588,7 +588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
@@ -597,12 +597,10 @@
     <col min="4" max="4" width="10.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -610,7 +608,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -625,10 +623,8 @@
         <v>18</v>
       </c>
       <c r="F2" s="10"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="10"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
         <v>2</v>
@@ -643,7 +639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -657,7 +653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -668,7 +664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>3</v>
       </c>
@@ -679,7 +675,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>4</v>
       </c>
@@ -690,7 +686,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>5</v>
       </c>
@@ -704,7 +700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>6</v>
       </c>
@@ -718,7 +714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>7</v>
       </c>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>!Table</t>
   </si>
@@ -123,6 +123,10 @@
       </rPr>
       <t>erLevel</t>
     </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Base</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -580,7 +584,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -588,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
@@ -647,10 +651,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -661,7 +665,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -726,6 +730,17 @@
       </c>
       <c r="E10" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>!Table</t>
   </si>
@@ -128,6 +128,12 @@
   <si>
     <t>StatDetail_MoveSpeed_Base</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_EvasionRate_Base</t>
+  </si>
+  <si>
+    <t>StatDetail_BlockRate_Base</t>
   </si>
 </sst>
 </file>
@@ -584,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -592,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="6"/>
@@ -741,6 +747,28 @@
       </c>
       <c r="D11" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -590,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -746,7 +746,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -590,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -590,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -590,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -657,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1">
         <v>2</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Character.xlsx
+++ b/Shared/XLS/Character.xlsx
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
